--- a/ig/test-tabs-svs/ValueSet-jdv-j402-type-droit-prestation-ms.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j402-type-droit-prestation-ms.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="171">
   <si>
     <t>Property</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>warning-draft</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j402-type-droit-prestation-ms|20260505120000</t>
   </si>
   <si>
     <t>Level</t>
@@ -846,7 +843,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -879,14 +876,6 @@
       </c>
       <c r="B4" t="s" s="2">
         <v>37</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -901,40 +890,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>41</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>45</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="F2" t="s" s="2">
         <v>15</v>
@@ -945,17 +934,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>15</v>
@@ -966,17 +955,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>15</v>
@@ -987,17 +976,17 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>55</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>15</v>
@@ -1008,17 +997,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>15</v>
@@ -1029,17 +1018,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>15</v>
@@ -1050,17 +1039,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>61</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>15</v>
@@ -1071,17 +1060,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>15</v>
@@ -1092,17 +1081,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>65</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>15</v>
@@ -1113,17 +1102,17 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>67</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>15</v>
@@ -1134,17 +1123,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>15</v>
@@ -1155,17 +1144,17 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>71</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>15</v>
@@ -1176,17 +1165,17 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>15</v>
@@ -1197,17 +1186,17 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>15</v>
@@ -1218,17 +1207,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>15</v>
@@ -1239,17 +1228,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>15</v>
@@ -1260,17 +1249,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>15</v>
@@ -1281,17 +1270,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>15</v>
@@ -1302,17 +1291,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>15</v>
@@ -1323,17 +1312,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>15</v>
@@ -1344,17 +1333,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>15</v>
@@ -1365,17 +1354,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>15</v>
@@ -1386,17 +1375,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E24" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>15</v>
@@ -1407,17 +1396,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>15</v>
@@ -1428,17 +1417,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E26" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>15</v>
@@ -1449,17 +1438,17 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E27" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>15</v>
@@ -1470,17 +1459,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>15</v>
@@ -1491,17 +1480,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E29" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>15</v>
@@ -1512,17 +1501,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E30" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>15</v>
@@ -1533,17 +1522,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E31" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>15</v>
@@ -1554,17 +1543,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E32" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>15</v>
@@ -1575,17 +1564,17 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>15</v>
@@ -1596,17 +1585,17 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>15</v>
@@ -1617,17 +1606,17 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E35" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>15</v>
@@ -1638,17 +1627,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>15</v>
@@ -1659,17 +1648,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E37" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>15</v>
@@ -1680,17 +1669,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E38" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>15</v>
@@ -1701,17 +1690,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E39" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>15</v>
@@ -1722,17 +1711,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E40" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>15</v>
@@ -1743,17 +1732,17 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E41" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>15</v>
@@ -1764,17 +1753,17 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E42" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="E42" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>15</v>
@@ -1785,17 +1774,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E43" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>15</v>
@@ -1806,17 +1795,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E44" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>15</v>
@@ -1827,17 +1816,17 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E45" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>15</v>
@@ -1848,17 +1837,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E46" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>15</v>
@@ -1869,17 +1858,17 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E47" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>15</v>
@@ -1890,17 +1879,17 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E48" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>15</v>
@@ -1911,17 +1900,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>15</v>
@@ -1932,17 +1921,17 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E50" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="E50" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>15</v>
@@ -1953,17 +1942,17 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E51" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="E51" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>15</v>
@@ -1974,17 +1963,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E52" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="E52" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>15</v>
@@ -1995,17 +1984,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E53" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="E53" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>15</v>
@@ -2016,17 +2005,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E54" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>15</v>
@@ -2037,17 +2026,17 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="E55" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>15</v>
@@ -2058,17 +2047,17 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E56" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="E56" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>15</v>
@@ -2079,17 +2068,17 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E57" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>15</v>
@@ -2100,17 +2089,17 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="E58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="E58" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>15</v>
@@ -2121,17 +2110,17 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="E59" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="E59" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>15</v>
@@ -2142,17 +2131,17 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>15</v>
@@ -2163,17 +2152,17 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="E61" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="E61" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>15</v>
@@ -2184,17 +2173,17 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="E62" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="E62" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>15</v>
@@ -2205,17 +2194,17 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="E63" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="E63" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>15</v>
